--- a/Employee_Reports_wi52/Eduard Embate Endonela Q0372.xlsx
+++ b/Employee_Reports_wi52/Eduard Embate Endonela Q0372.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -593,53 +593,53 @@
       <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>EWS EQ  (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-M-004</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>04-Oct-2024</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>04-Oct-2026</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -838,102 +838,102 @@
       <c r="K8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>TT+RA (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-M-007</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>25-Aug-2024</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>25-Aug-2026</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>CS-Hoist (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-M-001</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>27-Aug-2024</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>27-Aug-2026</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-323</v>
+        <v>-331</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-441</v>
+        <v>-449</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-527</v>
+        <v>-535</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-382</v>
+        <v>-390</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1464,41 +1464,41 @@
       <c r="K21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>04-Oct-2024</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>04-Oct-2026</t>
         </is>
       </c>
-      <c r="H22" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
